--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DACAE2F-DBC2-417F-B3CB-E2BA53EE2AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{334F9BC6-8DBD-4D07-8D22-4704CC42DB3A}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="data"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
   <si>
     <t>Email</t>
   </si>
@@ -88,9 +94,6 @@
     <t>Orders</t>
   </si>
   <si>
-    <t>orders</t>
-  </si>
-  <si>
     <t>private</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
     <t>Carts</t>
   </si>
   <si>
-    <t>carts</t>
-  </si>
-  <si>
     <t>Med</t>
   </si>
   <si>
@@ -167,37 +167,339 @@
   </si>
   <si>
     <t>test347</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>orders112</t>
+  </si>
+  <si>
+    <t>carts23</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -209,39 +511,209 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -252,10 +724,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -282,82 +754,116 @@
         <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -369,389 +875,381 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
-            </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930F31ED-EA35-44AD-8F2F-2616FE2164D9}">
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2">
+        <v>12542</v>
+      </c>
+      <c r="M2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="3">
-        <v>14543</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3">
+        <v>12542</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="3">
-        <v>14543</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4">
+        <v>12542</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="O4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
+      <c r="Q4" t="s">
         <v>48</v>
-      </c>
-      <c r="K4" s="3">
-        <v>14543</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
